--- a/docs/testing/Project Weekly Report_GroupName.xlsx
+++ b/docs/testing/Project Weekly Report_GroupName.xlsx
@@ -9,17 +9,18 @@
   </bookViews>
   <sheets>
     <sheet name="W1" sheetId="1" r:id="rId1"/>
-    <sheet name="W2" sheetId="2" r:id="rId49"/>
-    <sheet name="W3" sheetId="3" r:id="rId50"/>
-    <sheet name="W4" sheetId="4" r:id="rId51"/>
-    <sheet name="W5" sheetId="5" r:id="rId52"/>
-    <sheet name="W6" sheetId="6" r:id="rId53"/>
-    <sheet name="W7" sheetId="7" r:id="rId54"/>
-    <sheet name="W8" sheetId="8" r:id="rId55"/>
-    <sheet name="W9" sheetId="9" r:id="rId56"/>
-    <sheet name="W10" sheetId="10" r:id="rId57"/>
-    <sheet name="W11" sheetId="11" r:id="rId58"/>
-    <sheet name="W12" sheetId="12" r:id="rId59"/>
+    <sheet name="W2" sheetId="2" r:id="rId72"/>
+    <sheet name="W3" sheetId="3" r:id="rId73"/>
+    <sheet name="W4" sheetId="4" r:id="rId74"/>
+    <sheet name="W5" sheetId="5" r:id="rId75"/>
+    <sheet name="W6" sheetId="6" r:id="rId76"/>
+    <sheet name="W7" sheetId="7" r:id="rId77"/>
+    <sheet name="W8" sheetId="8" r:id="rId78"/>
+    <sheet name="W9" sheetId="9" r:id="rId79"/>
+    <sheet name="W10" sheetId="10" r:id="rId80"/>
+    <sheet name="W11" sheetId="11" r:id="rId81"/>
+    <sheet name="W12" sheetId="12" r:id="rId82"/>
+    <sheet name="W13" sheetId="13" r:id="rId83"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
@@ -1525,12 +1526,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CI/CD pipeline</t>
+          <t xml:space="preserve">IAM service</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phat</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1552,12 +1553,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IAM service</t>
+          <t xml:space="preserve">Database schema</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khoa</t>
+          <t xml:space="preserve">Phat</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1770,7 +1771,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55 commits this week</t>
+          <t xml:space="preserve">66 commits this week</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1798,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 commits this week</t>
+          <t xml:space="preserve">21 commits this week</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1810,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CI/CD pipeline</t>
+          <t xml:space="preserve">IAM service</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phat</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1836,12 +1837,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IAM service</t>
+          <t xml:space="preserve">Database schema</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khoa</t>
+          <t xml:space="preserve">Phat</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1851,7 +1852,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 commits this week</t>
+          <t xml:space="preserve">18 commits this week</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1864,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Database schema</t>
+          <t xml:space="preserve">CI/CD pipeline</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1878,7 +1879,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 commits this week</t>
+          <t xml:space="preserve">18 commits this week</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1994,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 fix commits merged</t>
+          <t xml:space="preserve">24 fix commits merged</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2021,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 fix commits merged</t>
+          <t xml:space="preserve">12 fix commits merged</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2033,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defects raised in CI/CD pipeline</t>
+          <t xml:space="preserve">Defects raised in Schema</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2120,7 +2121,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web frontend</t>
+          <t xml:space="preserve">Appointment booking</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2147,12 +2148,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incremental updates</t>
+          <t xml:space="preserve">Web frontend</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phat</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2174,7 +2175,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Appointment booking</t>
+          <t xml:space="preserve">Web frontend</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2266,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" style="4" customWidth="1"/>
@@ -2360,12 +2361,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 commits this week</t>
+          <t xml:space="preserve">70 commits this week</t>
         </is>
       </c>
     </row>
@@ -2377,22 +2378,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web frontend</t>
+          <t xml:space="preserve">Appointment booking</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhan</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 commits this week</t>
+          <t xml:space="preserve">27 commits this week</t>
         </is>
       </c>
     </row>
@@ -2404,22 +2405,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incremental updates</t>
+          <t xml:space="preserve">Web frontend</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phat</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 commits this week</t>
+          <t xml:space="preserve">26 commits this week</t>
         </is>
       </c>
     </row>
@@ -2431,22 +2432,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Appointment booking</t>
+          <t xml:space="preserve">Web frontend</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khoa</t>
+          <t xml:space="preserve">Nhan</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 commits this week</t>
+          <t xml:space="preserve">26 commits this week</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2469,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 commits this week</t>
+          <t xml:space="preserve">24 commits this week</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2665,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Closed</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 fix commits merged</t>
+          <t xml:space="preserve">11 fix commits merged</t>
         </is>
       </c>
     </row>
@@ -2681,22 +2682,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defects raised in Seed data</t>
+          <t xml:space="preserve">Defects raised in Iam service</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhan</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Closed</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 fix commits merged</t>
+          <t xml:space="preserve">6 fix commits merged</t>
         </is>
       </c>
     </row>
@@ -2708,22 +2709,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defects raised in Core modules</t>
+          <t xml:space="preserve">Defects raised in Booking flow</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhan</t>
+          <t xml:space="preserve">Khoa</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Progress</t>
+          <t xml:space="preserve">Closed</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 fix commits merged</t>
+          <t xml:space="preserve">5 fix commits merged</t>
         </is>
       </c>
     </row>
@@ -2769,110 +2770,705 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">AI services (KYC OCR, booking assistant)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khoa</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planned for week 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Container orchestration</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planned for week 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planned for week 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CI/CD pipeline</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planned for week 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV. Other Project Matters/Suggestions</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Matter/Suggestions</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raised By</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report 6 - Installation &amp; User Guide submitted</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All members</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/07/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliverable milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Next deliverable: Report 7 - Final Report</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All members</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/08/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Due in 12 day(s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D8 D12:D14" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Pending, In Progress, Completed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="38.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="57.5" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROJECT REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEP490_G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/08/2026-09/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. Status Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Task</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In-charge</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes (Work Item in Details)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI services (KYC OCR, booking assistant)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khoa</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 commits this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Container orchestration</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 commits this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 commits this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CI/CD pipeline</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 commits this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project documentation</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinh</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 commits this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report 7 — final report assembly</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinh</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VII. Appendix reference list built from the document footnotes; acknowledgement and 43-entry acronym table drafted</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report 7 — 5%% use case selection</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinh</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UC-19, 49, 70, 75 and 58 selected with evidence; one per documented user-manual flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">II. Project Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes (Solution, Suggestion, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defects raised in Container orchestration</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 fix commits merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defects raised in CI/CD pipeline</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phat</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 fix commits merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defects raised in Clinical EMR service</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khoa</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 fix commit merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III. Next Week Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Work Item</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In-charge</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deadline</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes (Task Details, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Report 7 - Final Report</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">All members</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">14/08/2026</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Remaining deliverable</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">IV. Other Project Matters/Suggestions</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">#</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Project Matter/Suggestions</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Raised By</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Date</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Report 6 - Installation &amp; User Guide submitted</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Next deliverable: Report 7 - Final Report</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">All members</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31/07/2026</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deliverable milestone</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Next deliverable: Report 7 - Final Report</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">All members</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">14/08/2026</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Due in 12 day(s)</t>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Due in 5 day(s)</t>
         </is>
       </c>
     </row>
